--- a/RC40_Pinmap.xlsx
+++ b/RC40_Pinmap.xlsx
@@ -1438,7 +1438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38D0752-6C4A-40D7-A9B9-7CD12FA937BE}">
-  <dimension ref="B1:G162"/>
+  <dimension ref="B1:H162"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
@@ -1446,6 +1446,7 @@
     <col min="5" max="5" width="48.5" customWidth="1"/>
     <col min="6" max="6" width="16.375" style="17" customWidth="1"/>
     <col min="7" max="7" width="22.375" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="20.25">
@@ -1458,7 +1459,7 @@
       <c r="F1" s="22"/>
       <c r="G1" s="23"/>
     </row>
-    <row r="2" spans="2:7" ht="33">
+    <row r="2" spans="2:8" ht="33">
       <c r="B2" s="13" t="s">
         <v>130</v>
       </c>
@@ -1477,8 +1478,13 @@
       <c r="G2" s="13" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="33">
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="33">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1493,8 +1499,13 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="15"/>
-    </row>
-    <row r="4" spans="2:7" ht="33">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="33">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1509,8 +1520,13 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="15"/>
-    </row>
-    <row r="5" spans="2:7" ht="33">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="33">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1525,8 +1541,13 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="2:7" ht="33">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="33">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1541,8 +1562,13 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="2:7" ht="33">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="33">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -1557,8 +1583,13 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="2:7" ht="33">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="33">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -1573,8 +1604,13 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="15"/>
-    </row>
-    <row r="9" spans="2:7" ht="33">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="33">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
@@ -1589,8 +1625,13 @@
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="15"/>
-    </row>
-    <row r="10" spans="2:7" ht="33">
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="33">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
@@ -1605,8 +1646,13 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="15"/>
-    </row>
-    <row r="11" spans="2:7" ht="33">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="33">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1621,8 +1667,13 @@
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="15"/>
-    </row>
-    <row r="12" spans="2:7" ht="33">
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="33">
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1637,8 +1688,13 @@
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="15"/>
-    </row>
-    <row r="13" spans="2:7" ht="33">
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="33">
       <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
@@ -1653,8 +1709,13 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="15"/>
-    </row>
-    <row r="14" spans="2:7" ht="49.5">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="49.5">
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
@@ -1669,8 +1730,13 @@
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="15"/>
-    </row>
-    <row r="15" spans="2:7">
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="2:8">
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1685,8 +1751,13 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="2:7">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="2:8">
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
@@ -1701,8 +1772,13 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="15"/>
-    </row>
-    <row r="17" spans="2:7" ht="33">
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="33">
       <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
@@ -1717,8 +1793,13 @@
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="15"/>
-    </row>
-    <row r="18" spans="2:7" ht="33">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="33">
       <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1733,8 +1814,13 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="15"/>
-    </row>
-    <row r="19" spans="2:7" ht="33">
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="33">
       <c r="B19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1749,8 +1835,13 @@
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="15"/>
-    </row>
-    <row r="20" spans="2:7" ht="33">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="33">
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1765,8 +1856,13 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="15"/>
-    </row>
-    <row r="21" spans="2:7" ht="33">
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="33">
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1781,8 +1877,13 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="15"/>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="2:8">
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
@@ -1797,8 +1898,13 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
       <c r="B23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1813,8 +1919,13 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="15"/>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24" s="3" t="s">
         <v>21</v>
       </c>
@@ -1829,8 +1940,13 @@
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="15"/>
-    </row>
-    <row r="25" spans="2:7">
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
       <c r="B25" s="3" t="s">
         <v>22</v>
       </c>
@@ -1845,8 +1961,13 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="15"/>
-    </row>
-    <row r="26" spans="2:7">
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
       <c r="B26" s="3" t="s">
         <v>23</v>
       </c>
@@ -1861,8 +1982,13 @@
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="15"/>
-    </row>
-    <row r="27" spans="2:7">
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
@@ -1877,8 +2003,13 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="15"/>
-    </row>
-    <row r="28" spans="2:7">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
       <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
@@ -1893,8 +2024,13 @@
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
       <c r="B29" s="3" t="s">
         <v>26</v>
       </c>
@@ -1909,8 +2045,13 @@
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="15"/>
-    </row>
-    <row r="30" spans="2:7">
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
       <c r="B30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1925,8 +2066,13 @@
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="15"/>
-    </row>
-    <row r="31" spans="2:7" ht="33">
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="33">
       <c r="B31" s="3" t="s">
         <v>28</v>
       </c>
@@ -1941,8 +2087,13 @@
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="15"/>
-    </row>
-    <row r="32" spans="2:7" ht="33">
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="33">
       <c r="B32" s="3" t="s">
         <v>29</v>
       </c>
@@ -1957,8 +2108,13 @@
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="15"/>
-    </row>
-    <row r="33" spans="2:7" ht="33">
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="33">
       <c r="B33" s="3" t="s">
         <v>30</v>
       </c>
@@ -1973,8 +2129,13 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="15"/>
-    </row>
-    <row r="34" spans="2:7" ht="33">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="33">
       <c r="B34" s="3" t="s">
         <v>31</v>
       </c>
@@ -1989,8 +2150,13 @@
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="15"/>
-    </row>
-    <row r="35" spans="2:7" ht="33">
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="33">
       <c r="B35" s="3" t="s">
         <v>32</v>
       </c>
@@ -2005,8 +2171,13 @@
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="15"/>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
       <c r="B36" s="3" t="s">
         <v>33</v>
       </c>
@@ -2021,8 +2192,13 @@
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="15"/>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
       <c r="B37" s="3" t="s">
         <v>34</v>
       </c>
@@ -2037,8 +2213,13 @@
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="15"/>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
       <c r="B38" s="3" t="s">
         <v>35</v>
       </c>
@@ -2053,8 +2234,13 @@
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="15"/>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
       <c r="B39" s="3" t="s">
         <v>36</v>
       </c>
@@ -2069,8 +2255,13 @@
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="15"/>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
       <c r="B40" s="3" t="s">
         <v>37</v>
       </c>
@@ -2085,8 +2276,13 @@
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="15"/>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
       <c r="B41" s="3" t="s">
         <v>38</v>
       </c>
@@ -2101,8 +2297,13 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="15"/>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
       <c r="B42" s="3" t="s">
         <v>39</v>
       </c>
@@ -2117,8 +2318,13 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="15"/>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
       <c r="B43" s="3" t="s">
         <v>40</v>
       </c>
@@ -2133,8 +2339,13 @@
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="15"/>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
       <c r="B44" s="3" t="s">
         <v>41</v>
       </c>
@@ -2147,8 +2358,13 @@
       <c r="E44" s="1"/>
       <c r="F44" s="3"/>
       <c r="G44" s="15"/>
-    </row>
-    <row r="45" spans="2:7" ht="33">
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="33">
       <c r="B45" s="3" t="s">
         <v>42</v>
       </c>
@@ -2163,8 +2379,13 @@
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="15"/>
-    </row>
-    <row r="46" spans="2:7" ht="33">
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="33">
       <c r="B46" s="3" t="s">
         <v>43</v>
       </c>
@@ -2179,8 +2400,13 @@
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="15"/>
-    </row>
-    <row r="47" spans="2:7" ht="33">
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="33">
       <c r="B47" s="3" t="s">
         <v>44</v>
       </c>
@@ -2195,8 +2421,13 @@
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="15"/>
-    </row>
-    <row r="48" spans="2:7" ht="33">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="33">
       <c r="B48" s="3" t="s">
         <v>45</v>
       </c>
@@ -2211,8 +2442,13 @@
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="15"/>
-    </row>
-    <row r="49" spans="2:7" ht="33">
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="33">
       <c r="B49" s="3" t="s">
         <v>46</v>
       </c>
@@ -2227,8 +2463,13 @@
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="15"/>
-    </row>
-    <row r="50" spans="2:7" ht="33">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="33">
       <c r="B50" s="3" t="s">
         <v>47</v>
       </c>
@@ -2243,8 +2484,13 @@
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="15"/>
-    </row>
-    <row r="51" spans="2:7" ht="33">
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="33">
       <c r="B51" s="3" t="s">
         <v>48</v>
       </c>
@@ -2259,8 +2505,13 @@
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="15"/>
-    </row>
-    <row r="52" spans="2:7" ht="33">
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="33">
       <c r="B52" s="3" t="s">
         <v>49</v>
       </c>
@@ -2275,8 +2526,13 @@
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="15"/>
-    </row>
-    <row r="53" spans="2:7" ht="33">
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="33">
       <c r="B53" s="3" t="s">
         <v>50</v>
       </c>
@@ -2291,8 +2547,13 @@
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="15"/>
-    </row>
-    <row r="54" spans="2:7" ht="33">
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="33">
       <c r="B54" s="3" t="s">
         <v>51</v>
       </c>
@@ -2307,8 +2568,13 @@
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="15"/>
-    </row>
-    <row r="55" spans="2:7" ht="33">
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="33">
       <c r="B55" s="3" t="s">
         <v>52</v>
       </c>
@@ -2323,8 +2589,13 @@
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="15"/>
-    </row>
-    <row r="56" spans="2:7">
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
       <c r="B56" s="3" t="s">
         <v>53</v>
       </c>
@@ -2339,8 +2610,13 @@
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="15"/>
-    </row>
-    <row r="57" spans="2:7" ht="33">
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="33">
       <c r="B57" s="3" t="s">
         <v>54</v>
       </c>
@@ -2355,8 +2631,13 @@
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="15"/>
-    </row>
-    <row r="58" spans="2:7">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
       <c r="B58" s="3" t="s">
         <v>55</v>
       </c>
@@ -2369,8 +2650,13 @@
       <c r="E58" s="1"/>
       <c r="F58" s="3"/>
       <c r="G58" s="15"/>
-    </row>
-    <row r="59" spans="2:7">
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
       <c r="B59" s="3" t="s">
         <v>56</v>
       </c>
@@ -2385,8 +2671,13 @@
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="15"/>
-    </row>
-    <row r="60" spans="2:7" ht="33">
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="33">
       <c r="B60" s="3" t="s">
         <v>57</v>
       </c>
@@ -2401,8 +2692,13 @@
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="15"/>
-    </row>
-    <row r="61" spans="2:7" ht="33">
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="2:8" ht="33">
       <c r="B61" s="3" t="s">
         <v>58</v>
       </c>
@@ -2417,8 +2713,13 @@
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="15"/>
-    </row>
-    <row r="62" spans="2:7" ht="33">
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="33">
       <c r="B62" s="3" t="s">
         <v>59</v>
       </c>
@@ -2433,8 +2734,13 @@
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="15"/>
-    </row>
-    <row r="63" spans="2:7">
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
       <c r="B63" s="3" t="s">
         <v>60</v>
       </c>
@@ -2449,8 +2755,13 @@
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="15"/>
-    </row>
-    <row r="64" spans="2:7">
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
       <c r="B64" s="3" t="s">
         <v>61</v>
       </c>
@@ -2465,8 +2776,13 @@
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="15"/>
-    </row>
-    <row r="65" spans="2:7" ht="33">
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="33">
       <c r="B65" s="3" t="s">
         <v>62</v>
       </c>
@@ -2481,8 +2797,13 @@
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="15"/>
-    </row>
-    <row r="66" spans="2:7" ht="33">
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="33">
       <c r="B66" s="3" t="s">
         <v>63</v>
       </c>
@@ -2497,8 +2818,13 @@
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="15"/>
-    </row>
-    <row r="67" spans="2:7" ht="33">
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="2:8" ht="33">
       <c r="B67" s="3" t="s">
         <v>64</v>
       </c>
@@ -2513,8 +2839,13 @@
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="15"/>
-    </row>
-    <row r="68" spans="2:7" ht="33">
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="33">
       <c r="B68" s="3" t="s">
         <v>65</v>
       </c>
@@ -2529,8 +2860,13 @@
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="15"/>
-    </row>
-    <row r="69" spans="2:7" ht="33">
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="33">
       <c r="B69" s="3" t="s">
         <v>66</v>
       </c>
@@ -2545,8 +2881,13 @@
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="15"/>
-    </row>
-    <row r="70" spans="2:7">
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="2:8">
       <c r="B70" s="3" t="s">
         <v>67</v>
       </c>
@@ -2561,8 +2902,13 @@
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="15"/>
-    </row>
-    <row r="71" spans="2:7">
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="2:8">
       <c r="B71" s="3" t="s">
         <v>68</v>
       </c>
@@ -2577,8 +2923,13 @@
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="15"/>
-    </row>
-    <row r="72" spans="2:7">
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="2:8">
       <c r="B72" s="3" t="s">
         <v>69</v>
       </c>
@@ -2593,8 +2944,13 @@
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="15"/>
-    </row>
-    <row r="73" spans="2:7" ht="49.5">
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="2:8" ht="49.5">
       <c r="B73" s="3" t="s">
         <v>70</v>
       </c>
@@ -2609,8 +2965,13 @@
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="15"/>
-    </row>
-    <row r="74" spans="2:7" ht="33">
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="33">
       <c r="B74" s="3" t="s">
         <v>71</v>
       </c>
@@ -2625,8 +2986,13 @@
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="15"/>
-    </row>
-    <row r="75" spans="2:7">
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="2:8">
       <c r="B75" s="3" t="s">
         <v>72</v>
       </c>
@@ -2641,8 +3007,13 @@
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="15"/>
-    </row>
-    <row r="76" spans="2:7">
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
       <c r="B76" s="3" t="s">
         <v>73</v>
       </c>
@@ -2655,8 +3026,13 @@
       <c r="E76" s="1"/>
       <c r="F76" s="3"/>
       <c r="G76" s="15"/>
-    </row>
-    <row r="77" spans="2:7">
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
       <c r="B77" s="3" t="s">
         <v>74</v>
       </c>
@@ -2671,8 +3047,13 @@
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="15"/>
-    </row>
-    <row r="78" spans="2:7">
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
       <c r="B78" s="3" t="s">
         <v>75</v>
       </c>
@@ -2687,8 +3068,13 @@
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="15"/>
-    </row>
-    <row r="79" spans="2:7">
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
       <c r="B79" s="3" t="s">
         <v>76</v>
       </c>
@@ -2703,8 +3089,13 @@
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="15"/>
-    </row>
-    <row r="80" spans="2:7">
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
       <c r="B80" s="3" t="s">
         <v>77</v>
       </c>
@@ -2719,8 +3110,13 @@
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="15"/>
-    </row>
-    <row r="81" spans="2:7">
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="3" t="s">
         <v>78</v>
       </c>
@@ -2735,8 +3131,13 @@
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="15"/>
-    </row>
-    <row r="82" spans="2:7">
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
       <c r="B82" s="3" t="s">
         <v>79</v>
       </c>
@@ -2751,8 +3152,13 @@
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="15"/>
-    </row>
-    <row r="83" spans="2:7">
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="2:8">
       <c r="B83" s="3" t="s">
         <v>80</v>
       </c>
@@ -2767,8 +3173,13 @@
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="15"/>
-    </row>
-    <row r="84" spans="2:7">
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="B84" s="3" t="s">
         <v>81</v>
       </c>
@@ -2781,8 +3192,13 @@
       <c r="E84" s="1"/>
       <c r="F84" s="3"/>
       <c r="G84" s="15"/>
-    </row>
-    <row r="85" spans="2:7">
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="2:8">
       <c r="B85" s="3" t="s">
         <v>82</v>
       </c>
@@ -2797,8 +3213,13 @@
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="15"/>
-    </row>
-    <row r="86" spans="2:7">
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="3" t="s">
         <v>83</v>
       </c>
@@ -2813,8 +3234,13 @@
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="15"/>
-    </row>
-    <row r="87" spans="2:7">
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="2:8">
       <c r="B87" s="3" t="s">
         <v>84</v>
       </c>
@@ -2829,8 +3255,13 @@
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="15"/>
-    </row>
-    <row r="88" spans="2:7">
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="3" t="s">
         <v>85</v>
       </c>
@@ -2845,8 +3276,13 @@
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="15"/>
-    </row>
-    <row r="89" spans="2:7">
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="2:8">
       <c r="B89" s="3" t="s">
         <v>86</v>
       </c>
@@ -2861,8 +3297,13 @@
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="15"/>
-    </row>
-    <row r="90" spans="2:7">
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="3" t="s">
         <v>87</v>
       </c>
@@ -2877,8 +3318,13 @@
       </c>
       <c r="F90" s="3"/>
       <c r="G90" s="15"/>
-    </row>
-    <row r="91" spans="2:7">
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="3" t="s">
         <v>88</v>
       </c>
@@ -2893,8 +3339,13 @@
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="15"/>
-    </row>
-    <row r="92" spans="2:7">
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" spans="2:8">
       <c r="B92" s="3" t="s">
         <v>89</v>
       </c>
@@ -2909,8 +3360,13 @@
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="15"/>
-    </row>
-    <row r="93" spans="2:7" ht="33">
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="2:8" ht="33">
       <c r="B93" s="3" t="s">
         <v>90</v>
       </c>
@@ -2925,8 +3381,13 @@
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="15"/>
-    </row>
-    <row r="94" spans="2:7">
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="3" t="s">
         <v>91</v>
       </c>
@@ -2941,8 +3402,13 @@
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="15"/>
-    </row>
-    <row r="95" spans="2:7">
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" spans="2:8">
       <c r="B95" s="3" t="s">
         <v>92</v>
       </c>
@@ -2957,8 +3423,13 @@
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="15"/>
-    </row>
-    <row r="96" spans="2:7">
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
       <c r="B96" s="3" t="s">
         <v>93</v>
       </c>
@@ -2973,8 +3444,13 @@
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="15"/>
-    </row>
-    <row r="97" spans="2:7">
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="2:8">
       <c r="B97" s="3" t="s">
         <v>94</v>
       </c>
@@ -2987,8 +3463,13 @@
       <c r="E97" s="1"/>
       <c r="F97" s="3"/>
       <c r="G97" s="15"/>
-    </row>
-    <row r="98" spans="2:7">
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="2:8">
       <c r="B98" s="3" t="s">
         <v>95</v>
       </c>
@@ -3003,8 +3484,13 @@
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="15"/>
-    </row>
-    <row r="99" spans="2:7">
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="2:8">
       <c r="B99" s="3" t="s">
         <v>96</v>
       </c>
@@ -3017,8 +3503,13 @@
       <c r="E99" s="1"/>
       <c r="F99" s="3"/>
       <c r="G99" s="15"/>
-    </row>
-    <row r="100" spans="2:7">
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="3" t="s">
         <v>97</v>
       </c>
@@ -3033,8 +3524,13 @@
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="15"/>
-    </row>
-    <row r="101" spans="2:7">
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="2:8">
       <c r="B101" s="3" t="s">
         <v>98</v>
       </c>
@@ -3049,8 +3545,13 @@
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="15"/>
-    </row>
-    <row r="102" spans="2:7">
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
       <c r="B102" s="3" t="s">
         <v>99</v>
       </c>
@@ -3065,8 +3566,13 @@
       </c>
       <c r="F102" s="3"/>
       <c r="G102" s="15"/>
-    </row>
-    <row r="103" spans="2:7">
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="3" t="s">
         <v>100</v>
       </c>
@@ -3081,8 +3587,13 @@
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="15"/>
-    </row>
-    <row r="104" spans="2:7">
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="2:8">
       <c r="B104" s="3" t="s">
         <v>101</v>
       </c>
@@ -3097,8 +3608,13 @@
       </c>
       <c r="F104" s="3"/>
       <c r="G104" s="15"/>
-    </row>
-    <row r="105" spans="2:7">
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="2:8">
       <c r="B105" s="3" t="s">
         <v>102</v>
       </c>
@@ -3113,8 +3629,13 @@
       </c>
       <c r="F105" s="3"/>
       <c r="G105" s="15"/>
-    </row>
-    <row r="106" spans="2:7">
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="3" t="s">
         <v>103</v>
       </c>
@@ -3129,8 +3650,13 @@
       </c>
       <c r="F106" s="3"/>
       <c r="G106" s="15"/>
-    </row>
-    <row r="107" spans="2:7">
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="2:8">
       <c r="B107" s="3" t="s">
         <v>104</v>
       </c>
@@ -3145,8 +3671,13 @@
       </c>
       <c r="F107" s="3"/>
       <c r="G107" s="15"/>
-    </row>
-    <row r="108" spans="2:7">
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="2:8">
       <c r="B108" s="3" t="s">
         <v>105</v>
       </c>
@@ -3161,8 +3692,13 @@
       </c>
       <c r="F108" s="3"/>
       <c r="G108" s="15"/>
-    </row>
-    <row r="109" spans="2:7">
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="2:8">
       <c r="B109" s="3" t="s">
         <v>106</v>
       </c>
@@ -3177,8 +3713,13 @@
       </c>
       <c r="F109" s="3"/>
       <c r="G109" s="15"/>
-    </row>
-    <row r="110" spans="2:7">
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="2:8">
       <c r="B110" s="3" t="s">
         <v>107</v>
       </c>
@@ -3193,8 +3734,13 @@
       </c>
       <c r="F110" s="3"/>
       <c r="G110" s="15"/>
-    </row>
-    <row r="111" spans="2:7" ht="33">
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="2:8" ht="33">
       <c r="B111" s="3" t="s">
         <v>108</v>
       </c>
@@ -3209,8 +3755,13 @@
       </c>
       <c r="F111" s="3"/>
       <c r="G111" s="15"/>
-    </row>
-    <row r="112" spans="2:7">
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="2:8">
       <c r="B112" s="3" t="s">
         <v>109</v>
       </c>
@@ -3225,8 +3776,13 @@
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="15"/>
-    </row>
-    <row r="113" spans="2:7">
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" spans="2:8">
       <c r="B113" s="3" t="s">
         <v>110</v>
       </c>
@@ -3241,8 +3797,13 @@
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="15"/>
-    </row>
-    <row r="114" spans="2:7">
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="2:8">
       <c r="B114" s="3" t="s">
         <v>111</v>
       </c>
@@ -3257,8 +3818,13 @@
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="15"/>
-    </row>
-    <row r="115" spans="2:7">
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="2:8">
       <c r="B115" s="3" t="s">
         <v>112</v>
       </c>
@@ -3273,8 +3839,13 @@
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="15"/>
-    </row>
-    <row r="116" spans="2:7">
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="2:8">
       <c r="B116" s="3" t="s">
         <v>113</v>
       </c>
@@ -3289,8 +3860,13 @@
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="15"/>
-    </row>
-    <row r="117" spans="2:7" ht="33">
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="2:8" ht="33">
       <c r="B117" s="3" t="s">
         <v>114</v>
       </c>
@@ -3305,8 +3881,13 @@
       </c>
       <c r="F117" s="3"/>
       <c r="G117" s="15"/>
-    </row>
-    <row r="118" spans="2:7" ht="33">
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" spans="2:8" ht="33">
       <c r="B118" s="3" t="s">
         <v>115</v>
       </c>
@@ -3321,8 +3902,13 @@
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="15"/>
-    </row>
-    <row r="119" spans="2:7" ht="33">
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" spans="2:8" ht="33">
       <c r="B119" s="3" t="s">
         <v>116</v>
       </c>
@@ -3337,8 +3923,13 @@
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="15"/>
-    </row>
-    <row r="120" spans="2:7" ht="33">
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" spans="2:8" ht="33">
       <c r="B120" s="3" t="s">
         <v>117</v>
       </c>
@@ -3353,8 +3944,13 @@
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="15"/>
-    </row>
-    <row r="121" spans="2:7" ht="33">
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" spans="2:8" ht="33">
       <c r="B121" s="3" t="s">
         <v>118</v>
       </c>
@@ -3369,8 +3965,13 @@
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="15"/>
-    </row>
-    <row r="122" spans="2:7" ht="33">
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="2:8" ht="33">
       <c r="B122" s="3" t="s">
         <v>119</v>
       </c>
@@ -3385,8 +3986,13 @@
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="15"/>
-    </row>
-    <row r="123" spans="2:7" ht="33">
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="2:8" ht="33">
       <c r="B123" s="3" t="s">
         <v>120</v>
       </c>
@@ -3401,8 +4007,13 @@
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="15"/>
-    </row>
-    <row r="124" spans="2:7" ht="33">
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="2:8" ht="33">
       <c r="B124" s="3" t="s">
         <v>121</v>
       </c>
@@ -3417,6 +4028,11 @@
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="15"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="125" spans="2:7" ht="20.25">
       <c r="B125" s="21" t="s">
@@ -3987,11 +4603,52 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E127:E131"/>
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B1:H1"/>
     <mergeCell ref="B149:G149"/>
     <mergeCell ref="B125:G125"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="13">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Use" error="ON 또는 OFF를 선택하세요." promptTitle="Use" prompt="ON: HwInp/HwOutp에 생성, OFF: Unused에 생성" sqref="H3:H124">
+      <formula1>"ON,OFF"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C22 C78 C90">
+      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C23:C25">
+      <formula1>"Frequency,DigitalSignal,AnalogSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C36:C39">
+      <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C43">
+      <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,Frequency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C75 C94 C104">
+      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency,SENTSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C79">
+      <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C82 C95 C101:C102">
+      <formula1>"Frequency,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,SENTSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C83 C96 C98 C105">
+      <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,Frequency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C85:C89">
+      <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C91:C92 C108:C110">
+      <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal,CurrentSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C100 C103">
+      <formula1>"SENTSignal,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,Frequency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C107">
+      <formula1>"PWMSignal,DigitalSignal,AnalogSignal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/RC40_Pinmap.xlsx
+++ b/RC40_Pinmap.xlsx
@@ -1893,8 +1893,10 @@
       <c r="D22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>192</v>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Digital, Voltage, Frequency, Resistance</t>
+        </is>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="15"/>
@@ -1914,8 +1916,10 @@
       <c r="D23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>195</v>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Digital, Voltage, Frequency, Resistance</t>
+        </is>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="15"/>
@@ -1935,8 +1939,10 @@
       <c r="D24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>195</v>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Digital, Voltage, Frequency, Resistance</t>
+        </is>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="15"/>
@@ -1956,8 +1962,10 @@
       <c r="D25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>195</v>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Digital, Voltage, Frequency, Resistance</t>
+        </is>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="15"/>
@@ -3002,8 +3010,10 @@
       <c r="D75" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>194</v>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Digital, Voltage, Current, Frequency, DSM1/DST1</t>
+        </is>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="15"/>
@@ -4608,15 +4618,15 @@
     <mergeCell ref="B125:G125"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="13">
+  <dataValidations count="14">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Use" error="ON 또는 OFF를 선택하세요." promptTitle="Use" prompt="ON: HwInp/HwOutp에 생성, OFF: Unused에 생성" sqref="H3:H124">
       <formula1>"ON,OFF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C22 C78 C90">
-      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C22">
+      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C23:C25">
-      <formula1>"Frequency,DigitalSignal,AnalogSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
+      <formula1>"Frequency,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C36:C39">
       <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
@@ -4624,8 +4634,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C43">
       <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,Frequency"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C75 C94 C104">
-      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency,SENTSignal"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C75 C83 C96 C98 C105">
+      <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,Frequency"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C78 C90">
+      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C79">
       <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal"</formula1>
@@ -4633,14 +4646,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C82 C95 C101:C102">
       <formula1>"Frequency,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,SENTSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C83 C96 C98 C105">
-      <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,Frequency"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C85:C89">
       <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C91:C92 C108:C110">
       <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal,CurrentSignal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C94 C104">
+      <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency,SENTSignal"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C100 C103">
       <formula1>"SENTSignal,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,Frequency"</formula1>

--- a/RC40_Pinmap.xlsx
+++ b/RC40_Pinmap.xlsx
@@ -2758,8 +2758,10 @@
       <c r="D63" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>191</v>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="15"/>
@@ -3052,8 +3054,10 @@
       <c r="D77" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>191</v>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="15"/>
@@ -3115,8 +3119,10 @@
       <c r="D80" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>191</v>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="15"/>
@@ -3781,8 +3787,10 @@
       <c r="D112" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>191</v>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F112" s="3"/>
       <c r="G112" s="15"/>
@@ -3802,8 +3810,10 @@
       <c r="D113" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>191</v>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F113" s="3"/>
       <c r="G113" s="15"/>
@@ -3823,8 +3833,10 @@
       <c r="D114" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>191</v>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F114" s="3"/>
       <c r="G114" s="15"/>
@@ -3844,8 +3856,10 @@
       <c r="D115" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>191</v>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F115" s="3"/>
       <c r="G115" s="15"/>
@@ -3865,8 +3879,10 @@
       <c r="D116" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>191</v>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>Pull-Up_32V</t>
+        </is>
       </c>
       <c r="F116" s="3"/>
       <c r="G116" s="15"/>

--- a/RC40_Pinmap.xlsx
+++ b/RC40_Pinmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seunghyeonnoh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seunghyeonnoh\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F100CE-D310-48E0-83DE-91A5C8B6D59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FABF116-1EE2-4639-93E0-0929AEE1B15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-14205" windowWidth="38640" windowHeight="21240" xr2:uid="{B47628C5-39C8-4AE7-9AE4-FD4D8F41738D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12735" xr2:uid="{B47628C5-39C8-4AE7-9AE4-FD4D8F41738D}"/>
   </bookViews>
   <sheets>
     <sheet name="GW1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="280">
   <si>
     <t>A01</t>
   </si>
@@ -700,10 +700,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Digital/Analog/Resistance</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Digital, Voltage, Current, Frequency, DSM1/DST1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -849,6 +845,208 @@
   <si>
     <t>Pin Assignment
 (MASAR)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>Digital, Voltage, Frequency, Resistance</t>
+  </si>
+  <si>
+    <t>Pull-Up_32V</t>
+  </si>
+  <si>
+    <t>Digital, Voltage, Current, Frequency, DSM1/DST1</t>
+  </si>
+  <si>
+    <t>PWR_LED_FAULT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_LED_MN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_LED_RM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_LED_CONN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_LED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGN_COM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_GRLY_HS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OUT_PWR_PDU1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGN_GA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGN_CRR</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGN_RT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGN_BRK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WU_SU</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENG_INHBIT_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENG_INHBIT_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MODE_MN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MODE_RM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_SIG1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_SIG2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_DA2_PWM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>APP_DA1_PWM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL_SHFT_SEL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL_SHFT_DN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL_SHFT_UP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GL_SHFT_PK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_CHSS2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_CHSS1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_GS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND_CHSS2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND_CHSS1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND_GS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEYON</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_AP_VCC2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWR_AP_VCC1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND_AP_GND2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GND_AP_GND1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCAN_H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCAN_L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCAN_H</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCAN_L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnalogSignal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyOn</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
+    <t>K24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Switch-On Signal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CHSS-KEY-M-#1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -893,7 +1091,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,6 +1113,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,7 +1226,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1039,9 +1243,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1">
@@ -1095,6 +1296,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1102,6 +1306,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1438,50 +1651,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38D0752-6C4A-40D7-A9B9-7CD12FA937BE}">
-  <dimension ref="B1:H162"/>
+  <dimension ref="B1:H163"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="48.5" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="17" customWidth="1"/>
-    <col min="7" max="7" width="22.375" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="16" customWidth="1"/>
+    <col min="7" max="7" width="22.375" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="20.25">
-      <c r="B1" s="21" t="s">
+    <row r="1" spans="2:8" ht="20.25">
+      <c r="B1" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="2:8" ht="33">
+      <c r="B2" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23"/>
-    </row>
-    <row r="2" spans="2:8" ht="33">
-      <c r="B2" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>228</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
       </c>
     </row>
     <row r="3" spans="2:8" ht="33">
@@ -1498,11 +1710,9 @@
         <v>138</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G3" s="14"/>
+      <c r="H3" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="33">
@@ -1519,11 +1729,9 @@
         <v>141</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G4" s="14"/>
+      <c r="H4" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="33">
@@ -1539,12 +1747,12 @@
       <c r="E5" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F5" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33">
@@ -1561,11 +1769,9 @@
         <v>150</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G6" s="14"/>
+      <c r="H6" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33">
@@ -1581,12 +1787,12 @@
       <c r="E7" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F7" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33">
@@ -1602,12 +1808,10 @@
       <c r="E8" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33">
@@ -1624,11 +1828,9 @@
         <v>140</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G9" s="14"/>
+      <c r="H9" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33">
@@ -1645,11 +1847,9 @@
         <v>140</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G10" s="14"/>
+      <c r="H10" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33">
@@ -1666,11 +1866,9 @@
         <v>141</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G11" s="14"/>
+      <c r="H11" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33">
@@ -1687,11 +1885,9 @@
         <v>137</v>
       </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G12" s="14"/>
+      <c r="H12" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33">
@@ -1708,11 +1904,9 @@
         <v>138</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G13" s="14"/>
+      <c r="H13" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="49.5">
@@ -1729,11 +1923,9 @@
         <v>139</v>
       </c>
       <c r="F14" s="3"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G14" s="14"/>
+      <c r="H14" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="2:8">
@@ -1750,11 +1942,9 @@
         <v>191</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G15" s="14"/>
+      <c r="H15" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="2:8">
@@ -1771,11 +1961,9 @@
         <v>190</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G16" s="14"/>
+      <c r="H16" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="33">
@@ -1792,11 +1980,9 @@
         <v>138</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G17" s="14"/>
+      <c r="H17" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="33">
@@ -1813,11 +1999,9 @@
         <v>141</v>
       </c>
       <c r="F18" s="3"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G18" s="14"/>
+      <c r="H18" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="33">
@@ -1834,11 +2018,9 @@
         <v>136</v>
       </c>
       <c r="F19" s="3"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G19" s="14"/>
+      <c r="H19" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="33">
@@ -1854,12 +2036,12 @@
       <c r="E20" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F20" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="G20" s="14"/>
+      <c r="H20" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="33">
@@ -1875,12 +2057,12 @@
       <c r="E21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F21" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="2:8">
@@ -1893,17 +2075,13 @@
       <c r="D22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>Digital, Voltage, Frequency, Resistance</t>
-        </is>
+      <c r="E22" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G22" s="14"/>
+      <c r="H22" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="23" spans="2:8">
@@ -1916,17 +2094,13 @@
       <c r="D23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>Digital, Voltage, Frequency, Resistance</t>
-        </is>
+      <c r="E23" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G23" s="14"/>
+      <c r="H23" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="2:8">
@@ -1939,17 +2113,13 @@
       <c r="D24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>Digital, Voltage, Frequency, Resistance</t>
-        </is>
+      <c r="E24" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G24" s="14"/>
+      <c r="H24" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="2:8">
@@ -1962,17 +2132,13 @@
       <c r="D25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>Digital, Voltage, Frequency, Resistance</t>
-        </is>
+      <c r="E25" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G25" s="14"/>
+      <c r="H25" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="2:8">
@@ -1989,11 +2155,9 @@
         <v>191</v>
       </c>
       <c r="F26" s="3"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G26" s="14"/>
+      <c r="H26" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="2:8">
@@ -2010,11 +2174,9 @@
         <v>191</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G27" s="14"/>
+      <c r="H27" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="28" spans="2:8">
@@ -2031,11 +2193,9 @@
         <v>191</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G28" s="14"/>
+      <c r="H28" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="2:8">
@@ -2052,11 +2212,9 @@
         <v>190</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G29" s="14"/>
+      <c r="H29" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="2:8">
@@ -2073,11 +2231,9 @@
         <v>190</v>
       </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G30" s="14"/>
+      <c r="H30" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="33">
@@ -2093,12 +2249,12 @@
       <c r="E31" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F31" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="33">
@@ -2115,11 +2271,9 @@
         <v>148</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G32" s="14"/>
+      <c r="H32" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="33">
@@ -2135,12 +2289,12 @@
       <c r="E33" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F33" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="G33" s="14"/>
+      <c r="H33" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="33">
@@ -2157,11 +2311,9 @@
         <v>148</v>
       </c>
       <c r="F34" s="3"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G34" s="14"/>
+      <c r="H34" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="33">
@@ -2178,11 +2330,9 @@
         <v>148</v>
       </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G35" s="14"/>
+      <c r="H35" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="2:8">
@@ -2196,14 +2346,12 @@
         <v>126</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F36" s="3"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G36" s="14"/>
+      <c r="H36" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="2:8">
@@ -2217,14 +2365,12 @@
         <v>126</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F37" s="3"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G37" s="14"/>
+      <c r="H37" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="2:8">
@@ -2238,14 +2384,12 @@
         <v>126</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F38" s="3"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G38" s="14"/>
+      <c r="H38" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="2:8">
@@ -2259,14 +2403,12 @@
         <v>126</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G39" s="14"/>
+      <c r="H39" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="40" spans="2:8">
@@ -2283,11 +2425,9 @@
         <v>191</v>
       </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G40" s="14"/>
+      <c r="H40" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="2:8">
@@ -2304,11 +2444,9 @@
         <v>191</v>
       </c>
       <c r="F41" s="3"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G41" s="14"/>
+      <c r="H41" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="2:8">
@@ -2325,11 +2463,9 @@
         <v>191</v>
       </c>
       <c r="F42" s="3"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G42" s="14"/>
+      <c r="H42" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="2:8">
@@ -2343,14 +2479,12 @@
         <v>126</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F43" s="3"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G43" s="14"/>
+      <c r="H43" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="44" spans="2:8">
@@ -2365,11 +2499,9 @@
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="3"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G44" s="14"/>
+      <c r="H44" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="33">
@@ -2386,11 +2518,9 @@
         <v>148</v>
       </c>
       <c r="F45" s="3"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G45" s="14"/>
+      <c r="H45" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="33">
@@ -2407,11 +2537,9 @@
         <v>148</v>
       </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G46" s="14"/>
+      <c r="H46" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="33">
@@ -2427,12 +2555,12 @@
       <c r="E47" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F47" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="G47" s="14"/>
+      <c r="H47" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="33">
@@ -2449,11 +2577,9 @@
         <v>149</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G48" s="14"/>
+      <c r="H48" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="49" spans="2:8" ht="33">
@@ -2470,11 +2596,9 @@
         <v>151</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G49" s="14"/>
+      <c r="H49" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="2:8" ht="33">
@@ -2491,11 +2615,9 @@
         <v>148</v>
       </c>
       <c r="F50" s="3"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G50" s="14"/>
+      <c r="H50" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="2:8" ht="33">
@@ -2512,11 +2634,9 @@
         <v>148</v>
       </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G51" s="14"/>
+      <c r="H51" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="2:8" ht="33">
@@ -2533,11 +2653,9 @@
         <v>148</v>
       </c>
       <c r="F52" s="3"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G52" s="14"/>
+      <c r="H52" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="53" spans="2:8" ht="33">
@@ -2554,11 +2672,9 @@
         <v>148</v>
       </c>
       <c r="F53" s="3"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G53" s="14"/>
+      <c r="H53" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="2:8" ht="33">
@@ -2575,11 +2691,9 @@
         <v>138</v>
       </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G54" s="14"/>
+      <c r="H54" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="2:8" ht="33">
@@ -2596,11 +2710,9 @@
         <v>138</v>
       </c>
       <c r="F55" s="3"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G55" s="14"/>
+      <c r="H55" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="2:8">
@@ -2617,11 +2729,9 @@
         <v>190</v>
       </c>
       <c r="F56" s="3"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G56" s="14"/>
+      <c r="H56" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="57" spans="2:8" ht="33">
@@ -2638,11 +2748,9 @@
         <v>143</v>
       </c>
       <c r="F57" s="3"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G57" s="14"/>
+      <c r="H57" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -2657,11 +2765,9 @@
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="3"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G58" s="14"/>
+      <c r="H58" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -2675,14 +2781,12 @@
         <v>126</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F59" s="3"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G59" s="14"/>
+      <c r="H59" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="60" spans="2:8" ht="33">
@@ -2698,12 +2802,12 @@
       <c r="E60" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F60" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="G60" s="14"/>
+      <c r="H60" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="33">
@@ -2720,11 +2824,9 @@
         <v>142</v>
       </c>
       <c r="F61" s="3"/>
-      <c r="G61" s="15"/>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G61" s="14"/>
+      <c r="H61" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="2:8" ht="33">
@@ -2741,11 +2843,9 @@
         <v>142</v>
       </c>
       <c r="F62" s="3"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G62" s="14"/>
+      <c r="H62" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -2758,17 +2858,13 @@
       <c r="D63" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E63" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F63" s="3"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G63" s="14"/>
+      <c r="H63" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8">
@@ -2785,11 +2881,9 @@
         <v>190</v>
       </c>
       <c r="F64" s="3"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G64" s="14"/>
+      <c r="H64" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="65" spans="2:8" ht="33">
@@ -2805,12 +2899,12 @@
       <c r="E65" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F65" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="G65" s="14"/>
+      <c r="H65" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="2:8" ht="33">
@@ -2827,11 +2921,9 @@
         <v>147</v>
       </c>
       <c r="F66" s="3"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G66" s="14"/>
+      <c r="H66" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="2:8" ht="33">
@@ -2847,12 +2939,12 @@
       <c r="E67" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F67" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="G67" s="14"/>
+      <c r="H67" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="2:8" ht="33">
@@ -2868,12 +2960,12 @@
       <c r="E68" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F68" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="G68" s="14"/>
+      <c r="H68" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="69" spans="2:8" ht="33">
@@ -2889,12 +2981,12 @@
       <c r="E69" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F69" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="G69" s="14"/>
+      <c r="H69" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="2:8">
@@ -2907,15 +2999,15 @@
       <c r="D70" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F70" s="3"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="E70" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F70" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="G70" s="14"/>
+      <c r="H70" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="71" spans="2:8">
@@ -2929,14 +3021,14 @@
         <v>126</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F71" s="3"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>201</v>
+      </c>
+      <c r="F71" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="G71" s="14"/>
+      <c r="H71" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="2:8">
@@ -2950,14 +3042,14 @@
         <v>126</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>201</v>
+      </c>
+      <c r="F72" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="G72" s="14"/>
+      <c r="H72" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="49.5">
@@ -2974,11 +3066,9 @@
         <v>139</v>
       </c>
       <c r="F73" s="3"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G73" s="14"/>
+      <c r="H73" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="33">
@@ -2995,11 +3085,9 @@
         <v>142</v>
       </c>
       <c r="F74" s="3"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G74" s="14"/>
+      <c r="H74" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="2:8">
@@ -3012,17 +3100,13 @@
       <c r="D75" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>Digital, Voltage, Current, Frequency, DSM1/DST1</t>
-        </is>
+      <c r="E75" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="F75" s="3"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G75" s="14"/>
+      <c r="H75" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="2:8">
@@ -3037,11 +3121,9 @@
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G76" s="14"/>
+      <c r="H76" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="77" spans="2:8">
@@ -3049,22 +3131,20 @@
         <v>74</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>125</v>
+        <v>273</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
-      </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="E77" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F77" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="G77" s="14"/>
+      <c r="H77" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="78" spans="2:8">
@@ -3078,14 +3158,12 @@
         <v>126</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F78" s="3"/>
-      <c r="G78" s="15"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G78" s="14"/>
+      <c r="H78" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="79" spans="2:8">
@@ -3099,14 +3177,12 @@
         <v>126</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F79" s="3"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G79" s="14"/>
+      <c r="H79" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -3119,17 +3195,15 @@
       <c r="D80" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
-      </c>
-      <c r="F80" s="3"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="E80" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F80" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="G80" s="14"/>
+      <c r="H80" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -3146,11 +3220,9 @@
         <v>190</v>
       </c>
       <c r="F81" s="3"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G81" s="14"/>
+      <c r="H81" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -3164,14 +3236,12 @@
         <v>126</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F82" s="3"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G82" s="14"/>
+      <c r="H82" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -3185,14 +3255,12 @@
         <v>126</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F83" s="3"/>
-      <c r="G83" s="15"/>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G83" s="14"/>
+      <c r="H83" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -3207,11 +3275,9 @@
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="3"/>
-      <c r="G84" s="15"/>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G84" s="14"/>
+      <c r="H84" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="2:8">
@@ -3219,20 +3285,20 @@
         <v>82</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F85" s="3"/>
-      <c r="G85" s="15"/>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>194</v>
+      </c>
+      <c r="F85" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="G85" s="14"/>
+      <c r="H85" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -3240,20 +3306,20 @@
         <v>83</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F86" s="3"/>
-      <c r="G86" s="15"/>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>194</v>
+      </c>
+      <c r="F86" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="G86" s="14"/>
+      <c r="H86" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="87" spans="2:8">
@@ -3267,14 +3333,12 @@
         <v>126</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F87" s="3"/>
-      <c r="G87" s="15"/>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G87" s="14"/>
+      <c r="H87" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -3288,14 +3352,12 @@
         <v>126</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F88" s="3"/>
-      <c r="G88" s="15"/>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G88" s="14"/>
+      <c r="H88" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="89" spans="2:8">
@@ -3309,14 +3371,12 @@
         <v>126</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F89" s="3"/>
-      <c r="G89" s="15"/>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G89" s="14"/>
+      <c r="H89" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="2:8">
@@ -3330,14 +3390,12 @@
         <v>126</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F90" s="3"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G90" s="14"/>
+      <c r="H90" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -3351,14 +3409,12 @@
         <v>126</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F91" s="3"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G91" s="14"/>
+      <c r="H91" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="92" spans="2:8">
@@ -3372,14 +3428,12 @@
         <v>126</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F92" s="3"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G92" s="14"/>
+      <c r="H92" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="2:8" ht="33">
@@ -3396,11 +3450,9 @@
         <v>144</v>
       </c>
       <c r="F93" s="3"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G93" s="14"/>
+      <c r="H93" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -3414,14 +3466,12 @@
         <v>126</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F94" s="3"/>
-      <c r="G94" s="15"/>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G94" s="14"/>
+      <c r="H94" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="2:8">
@@ -3435,14 +3485,12 @@
         <v>126</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F95" s="3"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G95" s="14"/>
+      <c r="H95" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="96" spans="2:8">
@@ -3456,14 +3504,12 @@
         <v>126</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F96" s="3"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G96" s="14"/>
+      <c r="H96" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="2:8">
@@ -3478,11 +3524,9 @@
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="3"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G97" s="14"/>
+      <c r="H97" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="2:8">
@@ -3496,14 +3540,12 @@
         <v>126</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F98" s="3"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G98" s="14"/>
+      <c r="H98" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="99" spans="2:8">
@@ -3518,11 +3560,9 @@
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="3"/>
-      <c r="G99" s="15"/>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G99" s="14"/>
+      <c r="H99" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -3536,14 +3576,12 @@
         <v>126</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F100" s="3"/>
-      <c r="G100" s="15"/>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G100" s="14"/>
+      <c r="H100" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="2:8">
@@ -3557,14 +3595,12 @@
         <v>126</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F101" s="3"/>
-      <c r="G101" s="15"/>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G101" s="14"/>
+      <c r="H101" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="2:8">
@@ -3578,14 +3614,12 @@
         <v>126</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F102" s="3"/>
-      <c r="G102" s="15"/>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G102" s="14"/>
+      <c r="H102" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -3599,14 +3633,12 @@
         <v>126</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F103" s="3"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G103" s="14"/>
+      <c r="H103" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="104" spans="2:8">
@@ -3620,14 +3652,12 @@
         <v>126</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F104" s="3"/>
-      <c r="G104" s="15"/>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G104" s="14"/>
+      <c r="H104" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="2:8">
@@ -3641,14 +3671,12 @@
         <v>126</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F105" s="3"/>
-      <c r="G105" s="15"/>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G105" s="14"/>
+      <c r="H105" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -3662,14 +3690,12 @@
         <v>126</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F106" s="3"/>
-      <c r="G106" s="15"/>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G106" s="14"/>
+      <c r="H106" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="2:8">
@@ -3683,14 +3709,12 @@
         <v>123</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F107" s="3"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G107" s="14"/>
+      <c r="H107" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="108" spans="2:8">
@@ -3704,14 +3728,12 @@
         <v>126</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F108" s="3"/>
-      <c r="G108" s="15"/>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G108" s="14"/>
+      <c r="H108" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="109" spans="2:8">
@@ -3725,14 +3747,12 @@
         <v>126</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F109" s="3"/>
-      <c r="G109" s="15"/>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G109" s="14"/>
+      <c r="H109" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="110" spans="2:8">
@@ -3746,14 +3766,12 @@
         <v>126</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F110" s="3"/>
-      <c r="G110" s="15"/>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G110" s="14"/>
+      <c r="H110" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="111" spans="2:8" ht="33">
@@ -3769,12 +3787,10 @@
       <c r="E111" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F111" s="3"/>
-      <c r="G111" s="15"/>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="F111" s="7"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="112" spans="2:8">
@@ -3787,17 +3803,13 @@
       <c r="D112" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E112" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F112" s="3"/>
-      <c r="G112" s="15"/>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G112" s="14"/>
+      <c r="H112" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="2:8">
@@ -3810,17 +3822,13 @@
       <c r="D113" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E113" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F113" s="3"/>
-      <c r="G113" s="15"/>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G113" s="14"/>
+      <c r="H113" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="114" spans="2:8">
@@ -3833,17 +3841,13 @@
       <c r="D114" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E114" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F114" s="3"/>
-      <c r="G114" s="15"/>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G114" s="14"/>
+      <c r="H114" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="115" spans="2:8">
@@ -3856,17 +3860,13 @@
       <c r="D115" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E115" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F115" s="3"/>
-      <c r="G115" s="15"/>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G115" s="14"/>
+      <c r="H115" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="116" spans="2:8">
@@ -3879,17 +3879,13 @@
       <c r="D116" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>Pull-Up_32V</t>
-        </is>
+      <c r="E116" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F116" s="3"/>
-      <c r="G116" s="15"/>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G116" s="14"/>
+      <c r="H116" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="2:8" ht="33">
@@ -3903,14 +3899,14 @@
         <v>123</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F117" s="3"/>
-      <c r="G117" s="15"/>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>196</v>
+      </c>
+      <c r="F117" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="G117" s="14"/>
+      <c r="H117" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="118" spans="2:8" ht="33">
@@ -3924,14 +3920,14 @@
         <v>123</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="F118" s="3"/>
-      <c r="G118" s="15"/>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>196</v>
+      </c>
+      <c r="F118" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="G118" s="14"/>
+      <c r="H118" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="119" spans="2:8" ht="33">
@@ -3945,14 +3941,12 @@
         <v>123</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F119" s="3"/>
-      <c r="G119" s="15"/>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G119" s="14"/>
+      <c r="H119" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="120" spans="2:8" ht="33">
@@ -3966,14 +3960,12 @@
         <v>123</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F120" s="3"/>
-      <c r="G120" s="15"/>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+      <c r="G120" s="14"/>
+      <c r="H120" s="3" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="121" spans="2:8" ht="33">
@@ -3987,14 +3979,14 @@
         <v>123</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F121" s="3"/>
-      <c r="G121" s="15"/>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>195</v>
+      </c>
+      <c r="F121" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="G121" s="14"/>
+      <c r="H121" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="122" spans="2:8" ht="33">
@@ -4008,14 +4000,14 @@
         <v>123</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F122" s="3"/>
-      <c r="G122" s="15"/>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>195</v>
+      </c>
+      <c r="F122" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="G122" s="14"/>
+      <c r="H122" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="123" spans="2:8" ht="33">
@@ -4029,14 +4021,14 @@
         <v>123</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F123" s="3"/>
-      <c r="G123" s="15"/>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
+        <v>195</v>
+      </c>
+      <c r="F123" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="G123" s="14"/>
+      <c r="H123" s="3" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="124" spans="2:8" ht="33">
@@ -4050,207 +4042,223 @@
         <v>123</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F124" s="3"/>
-      <c r="G124" s="15"/>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" spans="2:7" ht="20.25">
-      <c r="B125" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F124" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="G124" s="14"/>
+      <c r="H124" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" ht="20.25">
+      <c r="B125" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="C125" s="22"/>
-      <c r="D125" s="22"/>
-      <c r="E125" s="22"/>
-      <c r="F125" s="22"/>
-      <c r="G125" s="23"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="13" t="s">
+      <c r="C125" s="21"/>
+      <c r="D125" s="21"/>
+      <c r="E125" s="21"/>
+      <c r="F125" s="21"/>
+      <c r="G125" s="22"/>
+    </row>
+    <row r="126" spans="2:8">
+      <c r="B126" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C126" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E126" s="13" t="s">
+      <c r="E126" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F126" s="13" t="s">
+      <c r="F126" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G126" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7">
+      <c r="G126" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8">
       <c r="B127" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E127" s="17" t="s">
+        <v>217</v>
+      </c>
+      <c r="F127" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="G127" s="14"/>
+    </row>
+    <row r="128" spans="2:8">
+      <c r="B128" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C128" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E127" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="F127" s="6"/>
-      <c r="G127" s="15"/>
-    </row>
-    <row r="128" spans="2:7">
-      <c r="B128" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D128" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E128" s="19"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="15"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="G128" s="14"/>
     </row>
     <row r="129" spans="2:7">
       <c r="B129" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C129" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D129" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E129" s="19"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="15"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="G129" s="14"/>
     </row>
     <row r="130" spans="2:7">
       <c r="B130" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E130" s="19"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="15"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="3"/>
+      <c r="G130" s="14"/>
     </row>
     <row r="131" spans="2:7">
       <c r="B131" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C131" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E131" s="20"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="15"/>
+      <c r="E131" s="19"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="14"/>
     </row>
     <row r="132" spans="2:7">
       <c r="B132" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C132" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E132" s="2"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="15"/>
+      <c r="F132" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="G132" s="14"/>
     </row>
     <row r="133" spans="2:7">
       <c r="B133" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C133" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E133" s="2"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="15"/>
+      <c r="F133" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="G133" s="14"/>
     </row>
     <row r="134" spans="2:7">
       <c r="B134" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C134" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E134" s="2"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="15"/>
+      <c r="F134" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="G134" s="14"/>
     </row>
     <row r="135" spans="2:7">
       <c r="B135" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C135" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D135" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E135" s="2"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="15"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="14"/>
     </row>
     <row r="136" spans="2:7">
       <c r="B136" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="E136" s="2"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="15"/>
-    </row>
-    <row r="137" spans="2:7" ht="28.5">
-      <c r="B137" s="5" t="s">
-        <v>185</v>
+      <c r="F136" s="3"/>
+      <c r="G136" s="14"/>
+    </row>
+    <row r="137" spans="2:7">
+      <c r="B137" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>179</v>
+        <v>274</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>180</v>
+        <v>277</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F137" s="6"/>
-      <c r="G137" s="15"/>
+        <v>278</v>
+      </c>
+      <c r="F137" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G137" s="14" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="138" spans="2:7" ht="28.5">
       <c r="B138" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>179</v>
@@ -4259,14 +4267,14 @@
         <v>180</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F138" s="6"/>
-      <c r="G138" s="15"/>
-    </row>
-    <row r="139" spans="2:7" ht="33">
-      <c r="B139" s="3" t="s">
-        <v>177</v>
+        <v>186</v>
+      </c>
+      <c r="F138" s="3"/>
+      <c r="G138" s="14"/>
+    </row>
+    <row r="139" spans="2:7" ht="28.5">
+      <c r="B139" s="5" t="s">
+        <v>182</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>179</v>
@@ -4274,15 +4282,15 @@
       <c r="D139" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E139" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F139" s="6"/>
-      <c r="G139" s="15"/>
+      <c r="E139" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F139" s="3"/>
+      <c r="G139" s="14"/>
     </row>
     <row r="140" spans="2:7" ht="33">
       <c r="B140" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>179</v>
@@ -4293,12 +4301,14 @@
       <c r="E140" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F140" s="6"/>
-      <c r="G140" s="15"/>
+      <c r="F140" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="G140" s="14"/>
     </row>
     <row r="141" spans="2:7" ht="33">
       <c r="B141" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>179</v>
@@ -4307,14 +4317,16 @@
         <v>180</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F141" s="6"/>
-      <c r="G141" s="15"/>
+        <v>181</v>
+      </c>
+      <c r="F141" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="G141" s="14"/>
     </row>
     <row r="142" spans="2:7" ht="33">
       <c r="B142" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>179</v>
@@ -4325,356 +4337,381 @@
       <c r="E142" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F142" s="6"/>
-      <c r="G142" s="15"/>
-    </row>
-    <row r="143" spans="2:7">
+      <c r="G142" s="14"/>
+    </row>
+    <row r="143" spans="2:7" ht="33">
       <c r="B143" s="3" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E143" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="F143" s="3"/>
-      <c r="G143" s="15"/>
+      <c r="G143" s="14"/>
     </row>
     <row r="144" spans="2:7">
       <c r="B144" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E144" s="1"/>
-      <c r="F144" s="3"/>
-      <c r="G144" s="15"/>
+      <c r="F144" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="G144" s="14"/>
     </row>
     <row r="145" spans="2:7">
       <c r="B145" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E145" s="1"/>
-      <c r="F145" s="3"/>
-      <c r="G145" s="15"/>
+      <c r="F145" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="G145" s="14"/>
     </row>
     <row r="146" spans="2:7">
       <c r="B146" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E146" s="1"/>
-      <c r="F146" s="3"/>
-      <c r="G146" s="15"/>
+      <c r="G146" s="14"/>
     </row>
     <row r="147" spans="2:7">
       <c r="B147" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="3"/>
-      <c r="G147" s="15"/>
+      <c r="G147" s="14"/>
     </row>
     <row r="148" spans="2:7">
       <c r="B148" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E148" s="1"/>
       <c r="F148" s="3"/>
-      <c r="G148" s="15"/>
-    </row>
-    <row r="149" spans="2:7" ht="20.25" customHeight="1">
-      <c r="B149" s="24" t="s">
+      <c r="G148" s="14"/>
+    </row>
+    <row r="149" spans="2:7">
+      <c r="B149" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E149" s="1"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="14"/>
+    </row>
+    <row r="150" spans="2:7" ht="20.25" customHeight="1">
+      <c r="B150" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25"/>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25"/>
-      <c r="G149" s="26"/>
-    </row>
-    <row r="150" spans="2:7">
-      <c r="B150" s="13" t="s">
+      <c r="C150" s="25"/>
+      <c r="D150" s="25"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="26"/>
+    </row>
+    <row r="151" spans="2:7">
+      <c r="B151" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C151" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D150" s="13" t="s">
+      <c r="D151" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E150" s="13" t="s">
+      <c r="E151" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F150" s="13" t="s">
+      <c r="F151" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="G150" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7">
-      <c r="B151" s="8" t="s">
+      <c r="G151" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="152" spans="2:7">
+      <c r="B152" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C152" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D151" s="9" t="s">
+      <c r="D152" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E151" s="10"/>
-      <c r="F151" s="9"/>
-      <c r="G151" s="15"/>
-    </row>
-    <row r="152" spans="2:7">
-      <c r="B152" s="8" t="s">
+      <c r="E152" s="9"/>
+      <c r="F152" s="8"/>
+      <c r="G152" s="14"/>
+    </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C153" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="D153" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E152" s="10"/>
-      <c r="F152" s="9"/>
-      <c r="G152" s="15"/>
-    </row>
-    <row r="153" spans="2:7">
-      <c r="B153" s="8" t="s">
+      <c r="E153" s="9"/>
+      <c r="F153" s="8"/>
+      <c r="G153" s="14"/>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C154" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D153" s="8" t="s">
+      <c r="D154" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E153" s="12" t="s">
+      <c r="E154" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F153" s="9"/>
-      <c r="G153" s="15"/>
-    </row>
-    <row r="154" spans="2:7">
-      <c r="B154" s="8" t="s">
+      <c r="F154" s="8"/>
+      <c r="G154" s="14"/>
+    </row>
+    <row r="155" spans="2:7">
+      <c r="B155" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C155" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D154" s="8" t="s">
+      <c r="D155" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E154" s="12" t="s">
+      <c r="E155" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F154" s="9"/>
-      <c r="G154" s="15"/>
-    </row>
-    <row r="155" spans="2:7">
-      <c r="B155" s="8" t="s">
+      <c r="F155" s="8"/>
+      <c r="G155" s="14"/>
+    </row>
+    <row r="156" spans="2:7">
+      <c r="B156" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C155" s="9" t="s">
+      <c r="C156" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D155" s="8" t="s">
+      <c r="D156" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="E156" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F155" s="9"/>
-      <c r="G155" s="15"/>
-    </row>
-    <row r="156" spans="2:7">
-      <c r="B156" s="8" t="s">
+      <c r="F156" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="G156" s="14"/>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="B157" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C156" s="9" t="s">
+      <c r="C157" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D156" s="8" t="s">
+      <c r="D157" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E156" s="10" t="s">
+      <c r="E157" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F156" s="9"/>
-      <c r="G156" s="15"/>
-    </row>
-    <row r="157" spans="2:7">
-      <c r="B157" s="8" t="s">
+      <c r="F157" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="G157" s="14"/>
+    </row>
+    <row r="158" spans="2:7">
+      <c r="B158" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C158" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D157" s="8" t="s">
+      <c r="D158" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E157" s="10" t="s">
+      <c r="E158" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F157" s="9"/>
-      <c r="G157" s="16"/>
-    </row>
-    <row r="158" spans="2:7">
-      <c r="B158" s="8" t="s">
+      <c r="F158" s="29"/>
+      <c r="G158" s="15"/>
+    </row>
+    <row r="159" spans="2:7">
+      <c r="B159" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C158" s="9" t="s">
+      <c r="C159" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="D158" s="8" t="s">
+      <c r="D159" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E158" s="10" t="s">
+      <c r="E159" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F158" s="9"/>
-      <c r="G158" s="16"/>
-    </row>
-    <row r="159" spans="2:7">
-      <c r="B159" s="8" t="s">
+      <c r="F159" s="8"/>
+      <c r="G159" s="15"/>
+    </row>
+    <row r="160" spans="2:7">
+      <c r="B160" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C160" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D159" s="8" t="s">
+      <c r="D160" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E159" s="12" t="s">
+      <c r="E160" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="F159" s="9"/>
-      <c r="G159" s="15"/>
-    </row>
-    <row r="160" spans="2:7">
-      <c r="B160" s="8" t="s">
+      <c r="F160" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="G160" s="14"/>
+    </row>
+    <row r="161" spans="2:7">
+      <c r="B161" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C160" s="9" t="s">
+      <c r="C161" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="D161" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E160" s="10" t="s">
+      <c r="E161" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F160" s="9"/>
-      <c r="G160" s="15"/>
-    </row>
-    <row r="161" spans="2:7">
-      <c r="B161" s="8" t="s">
+      <c r="F161" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="G161" s="14"/>
+    </row>
+    <row r="162" spans="2:7">
+      <c r="B162" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C162" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D161" s="9" t="s">
+      <c r="D162" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E161" s="10"/>
-      <c r="F161" s="9"/>
-      <c r="G161" s="15"/>
-    </row>
-    <row r="162" spans="2:7">
-      <c r="B162" s="8" t="s">
+      <c r="E162" s="9"/>
+      <c r="G162" s="14"/>
+    </row>
+    <row r="163" spans="2:7">
+      <c r="B163" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C162" s="9" t="s">
+      <c r="C163" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D162" s="9" t="s">
+      <c r="D163" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E162" s="10"/>
-      <c r="F162" s="9"/>
-      <c r="G162" s="15"/>
+      <c r="E163" s="9"/>
+      <c r="F163" s="8"/>
+      <c r="G163" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E127:E131"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B149:G149"/>
+    <mergeCell ref="B150:G150"/>
     <mergeCell ref="B125:G125"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="14">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Use" error="ON 또는 OFF를 선택하세요." promptTitle="Use" prompt="ON: HwInp/HwOutp에 생성, OFF: Unused에 생성" sqref="H3:H124">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Use" error="ON 또는 OFF를 선택하세요." promptTitle="Use" prompt="ON: HwInp/HwOutp에 생성, OFF: Unused에 생성" sqref="H3:H124" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"ON,OFF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C22" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C23:C25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C23:C25" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Frequency,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C36:C39">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C36:C39" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C43">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C43" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,Frequency"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C75 C83 C96 C98 C105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C75 C83 C96 C98 C105" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"AnalogSignal,DigitalSignal,CurrentSignal,Frequency"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C78 C90">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C78 C90" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C79">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C79" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C82 C95 C101:C102">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C82 C95 C101:C102" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>"Frequency,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,SENTSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C85:C89">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C85:C89" xr:uid="{00000000-0002-0000-0000-000009000000}">
       <formula1>"DigitalSignal,AnalogSignal,CurrentSignal,ResistanceMeasurementSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C91:C92 C108:C110">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C91:C92 C108:C110" xr:uid="{00000000-0002-0000-0000-00000A000000}">
       <formula1>"ResistanceMeasurementSignal,DigitalSignal,AnalogSignal,CurrentSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C94 C104">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C94 C104" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>"AnalogSignal,DigitalSignal,ResistanceMeasurementSignal,Frequency,SENTSignal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C100 C103">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C100 C103" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>"SENTSignal,DigitalSignal,AnalogSignal,ResistanceMeasurementSignal,Frequency"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C107">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Type" error="이 핀이 지원하는 기능 중에서 선택하세요." promptTitle="Multi-port" prompt="핀 기능을 선택하세요 (easyConfig와 일치시킬 것)" sqref="C107" xr:uid="{00000000-0002-0000-0000-00000D000000}">
       <formula1>"PWMSignal,DigitalSignal,AnalogSignal"</formula1>
     </dataValidation>
   </dataValidations>
